--- a/GRM_Data.xlsx
+++ b/GRM_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipTime Cloud\Hana Data Research\RawData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E615AD4-26DD-4AC7-8B96-5408509D4B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA127581-C23F-4D44-9609-48B88E0C8D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="1935" windowWidth="28800" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GRM별_지점코드" sheetId="15" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="345">
   <si>
     <t>G7189653</t>
   </si>
@@ -1059,9 +1059,6 @@
     <t>[4사업단] - 조수연</t>
   </si>
   <si>
-    <t>[4사업단] - 김정운</t>
-  </si>
-  <si>
     <t>[4사업단] - 남민화</t>
   </si>
   <si>
@@ -1081,6 +1078,10 @@
   </si>
   <si>
     <t>[직할사업단] - 전혜정/이호준/김민준</t>
+  </si>
+  <si>
+    <t>[4사업단] - 김정운</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1973,13 +1974,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200FDD0B-215F-4AD7-9180-9E2BD6BED19F}">
-  <dimension ref="A1:AG558"/>
+  <dimension ref="A1:Y558"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="25" width="10.125" style="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="49" t="s">
         <v>19</v>
       </c>
@@ -2056,108 +2057,84 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="49" t="s">
-        <v>35</v>
+        <v>320</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>37</v>
+        <v>321</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>38</v>
+        <v>322</v>
       </c>
       <c r="D2" s="49" t="s">
-        <v>36</v>
+        <v>323</v>
       </c>
       <c r="E2" s="49" t="s">
-        <v>40</v>
+        <v>324</v>
       </c>
       <c r="F2" s="49" t="s">
-        <v>41</v>
+        <v>325</v>
       </c>
       <c r="G2" s="49" t="s">
-        <v>50</v>
+        <v>326</v>
       </c>
       <c r="H2" s="49" t="s">
-        <v>39</v>
+        <v>327</v>
       </c>
       <c r="I2" s="49" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="J2" s="49" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="K2" s="49" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="L2" s="49" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="M2" s="49" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="N2" s="49" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="O2" s="49" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="P2" s="49" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="Q2" s="49" t="s">
-        <v>328</v>
-      </c>
-      <c r="R2" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="S2" s="49" t="s">
-        <v>330</v>
-      </c>
-      <c r="T2" s="49" t="s">
-        <v>331</v>
-      </c>
-      <c r="U2" s="49" t="s">
-        <v>332</v>
-      </c>
-      <c r="V2" s="49" t="s">
-        <v>333</v>
-      </c>
-      <c r="W2" s="49" t="s">
-        <v>334</v>
-      </c>
-      <c r="X2" s="49" t="s">
-        <v>335</v>
-      </c>
-      <c r="Y2" s="49" t="s">
         <v>336</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="R2" t="s">
+        <v>344</v>
+      </c>
+      <c r="S2" t="s">
         <v>337</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="T2" t="s">
         <v>338</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="U2" t="s">
         <v>339</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="V2" t="s">
         <v>340</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="W2" t="s">
         <v>341</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="X2" t="s">
         <v>342</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="Y2" t="s">
         <v>343</v>
       </c>
-      <c r="AG2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="49">
         <v>988956</v>
       </c>
@@ -2234,7 +2211,7 @@
         <v>998196</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="49">
         <v>980114</v>
       </c>
@@ -2311,7 +2288,7 @@
         <v>983048</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="49">
         <v>996401</v>
       </c>
@@ -2388,7 +2365,7 @@
         <v>998148</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="49">
         <v>991165</v>
       </c>
@@ -2465,7 +2442,7 @@
         <v>983049</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="49">
         <v>975145</v>
       </c>
@@ -2542,7 +2519,7 @@
         <v>983104</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="49">
         <v>986063</v>
       </c>
@@ -2619,7 +2596,7 @@
         <v>998172</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
         <v>940063</v>
       </c>
@@ -2696,7 +2673,7 @@
         <v>998005</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="49">
         <v>996021</v>
       </c>
@@ -2773,7 +2750,7 @@
         <v>998096</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>995325</v>
       </c>
@@ -2850,7 +2827,7 @@
         <v>998097</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="49">
         <v>955072</v>
       </c>
@@ -2927,7 +2904,7 @@
         <v>998144</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
         <v>955107</v>
       </c>
@@ -3004,7 +2981,7 @@
         <v>998149</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
         <v>982010</v>
       </c>
@@ -3081,7 +3058,7 @@
         <v>983047</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
         <v>993087</v>
       </c>
@@ -3158,7 +3135,7 @@
         <v>998195</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="49">
         <v>995109</v>
       </c>

--- a/GRM_Data.xlsx
+++ b/GRM_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipTime Cloud\Hana Data Research\RawData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA127581-C23F-4D44-9609-48B88E0C8D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD2A518-4D33-4D9F-B181-9E468D8DA051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="1935" windowWidth="28800" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GRM별_지점코드" sheetId="15" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="348">
   <si>
     <t>G7189653</t>
   </si>
@@ -1032,12 +1032,6 @@
     <t>[2사업단] - 신미지</t>
   </si>
   <si>
-    <t>[2사업단] - 2단신규1</t>
-  </si>
-  <si>
-    <t>[2사업단] - 2단신규2</t>
-  </si>
-  <si>
     <t>[3사업단] - 유재목</t>
   </si>
   <si>
@@ -1048,12 +1042,6 @@
   </si>
   <si>
     <t>[3사업단] - 최정민</t>
-  </si>
-  <si>
-    <t>[3사업단] - 3단신규1</t>
-  </si>
-  <si>
-    <t>[3사업단] - 3단신규2</t>
   </si>
   <si>
     <t>[4사업단] - 조수연</t>
@@ -1080,8 +1068,28 @@
     <t>[직할사업단] - 전혜정/이호준/김민준</t>
   </si>
   <si>
+    <t>G7247396</t>
+  </si>
+  <si>
+    <t>G7247402</t>
+  </si>
+  <si>
+    <t>G7247403</t>
+  </si>
+  <si>
+    <t>[2사업단] - 오영주</t>
+  </si>
+  <si>
+    <t>[2사업단] - 정지혜</t>
+  </si>
+  <si>
+    <t>[3사업단] - 이선미</t>
+  </si>
+  <si>
+    <t>[3사업단] - 조현주</t>
+  </si>
+  <si>
     <t>[4사업단] - 김정운</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1977,7 +1985,13 @@
   <dimension ref="A1:Y558"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="25" width="10.125" style="49" customWidth="1"/>
+    <col min="1" max="6" width="17.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.625" style="49" bestFit="1" customWidth="1"/>
+    <col min="8" max="20" width="17.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.625" style="49" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="21" style="49" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="35" style="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -2006,10 +2020,10 @@
         <v>0</v>
       </c>
       <c r="I1" s="49" t="s">
-        <v>268</v>
+        <v>340</v>
       </c>
       <c r="J1" s="49" t="s">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="K1" s="49" t="s">
         <v>27</v>
@@ -2027,7 +2041,7 @@
         <v>267</v>
       </c>
       <c r="P1" s="49" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="Q1" s="49" t="s">
         <v>2</v>
@@ -2083,55 +2097,55 @@
         <v>327</v>
       </c>
       <c r="I2" s="49" t="s">
+        <v>343</v>
+      </c>
+      <c r="J2" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="K2" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="J2" s="49" t="s">
+      <c r="L2" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="K2" s="49" t="s">
+      <c r="M2" s="49" t="s">
         <v>330</v>
       </c>
-      <c r="L2" s="49" t="s">
+      <c r="N2" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="M2" s="49" t="s">
+      <c r="O2" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="P2" s="49" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q2" s="49" t="s">
         <v>332</v>
       </c>
-      <c r="N2" s="49" t="s">
+      <c r="R2" t="s">
+        <v>347</v>
+      </c>
+      <c r="S2" t="s">
         <v>333</v>
       </c>
-      <c r="O2" s="49" t="s">
+      <c r="T2" t="s">
         <v>334</v>
       </c>
-      <c r="P2" s="49" t="s">
+      <c r="U2" t="s">
         <v>335</v>
       </c>
-      <c r="Q2" s="49" t="s">
+      <c r="V2" t="s">
         <v>336</v>
       </c>
-      <c r="R2" t="s">
-        <v>344</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="W2" t="s">
         <v>337</v>
       </c>
-      <c r="T2" t="s">
+      <c r="X2" t="s">
         <v>338</v>
       </c>
-      <c r="U2" t="s">
+      <c r="Y2" t="s">
         <v>339</v>
-      </c>
-      <c r="V2" t="s">
-        <v>340</v>
-      </c>
-      <c r="W2" t="s">
-        <v>341</v>
-      </c>
-      <c r="X2" t="s">
-        <v>342</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
